--- a/output/pdf_financials_xlsx/AFCC.H.xlsx
+++ b/output/pdf_financials_xlsx/AFCC.H.xlsx
@@ -1038,25 +1038,25 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.048748</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.291164</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.254364</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.323576</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.350778</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.157607</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1920,25 +1920,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.262131</v>
+        <v>0.213383</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.521968</v>
+        <v>-1.813132</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.521968</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.450433</v>
+        <v>-0.704797</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-4.358385</v>
+        <v>-4.681961</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.625227</v>
+        <v>0.274449</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.765034</v>
+        <v>0.6074270000000001</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>4.290878</v>
@@ -2028,25 +2028,25 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.262131</v>
+        <v>0.213383</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.521968</v>
+        <v>-1.813132</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.521968</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.450433</v>
+        <v>-0.704797</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-4.358385</v>
+        <v>-4.681961</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.625227</v>
+        <v>0.274449</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.765034</v>
+        <v>0.6074270000000001</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>4.290878</v>
@@ -2302,16 +2302,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.0137</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.55777</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.141237</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.233597</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>7.687652</v>
@@ -2323,28 +2323,28 @@
         <v>14.20884</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>30.50841</v>
+        <v>1.693972</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.172755</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>43.367038</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>27.806646</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.77011</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.237936</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.183585</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>26.132385</v>
       </c>
     </row>
     <row r="35">
@@ -2406,16 +2406,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.0137</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.55777</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.141237</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.233597</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>7.687652</v>
@@ -2427,28 +2427,28 @@
         <v>14.20884</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>30.50841</v>
+        <v>1.693972</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>2.172755</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>43.367038</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>27.806646</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.77011</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.237936</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.183585</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>26.132385</v>
       </c>
     </row>
     <row r="37">
@@ -3030,16 +3030,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.448832</v>
+        <v>3.435132</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>6.795333</v>
+        <v>6.237563</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>11.987003</v>
+        <v>11.845766</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>9.296801</v>
+        <v>9.063204000000001</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>1.068427</v>
@@ -3051,28 +3051,28 @@
         <v>0.739861</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0</v>
+        <v>0.790357</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.039264</v>
+        <v>0.866509</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>43.90973</v>
+        <v>0.542692</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>27.822891</v>
+        <v>0.016245</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>22.827229</v>
+        <v>21.057119</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>21.255055</v>
+        <v>21.017119</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>21.201417</v>
+        <v>21.017832</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>26.148583</v>
+        <v>0.016198</v>
       </c>
     </row>
     <row r="49">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
@@ -33709,7 +33709,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -38789,7 +38789,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -42136,7 +42136,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -42227,7 +42227,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -45067,7 +45067,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -45247,7 +45247,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -48048,7 +48048,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -50050,7 +50050,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -50143,7 +50143,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">

--- a/output/pdf_financials_xlsx/AFCC.H.xlsx
+++ b/output/pdf_financials_xlsx/AFCC.H.xlsx
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.002534</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.001522</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.213383</v>
+        <v>0.215917</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.813132</v>
+        <v>-1.81161</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.521968</v>
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.002534</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.001522</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0</v>
@@ -27333,7 +27333,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -28690,7 +28694,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -47597,7 +47605,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AFCC.H.xlsx
+++ b/output/pdf_financials_xlsx/AFCC.H.xlsx
@@ -752,46 +752,46 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.407521</v>
+        <v>0.480466</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.239026</v>
+        <v>0.344665</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.020064</v>
+        <v>0.081666</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.020988</v>
+        <v>0.069936</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.020358</v>
+        <v>0.070369</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.018831</v>
+        <v>0.073781</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0</v>
+        <v>0.031564</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0</v>
+        <v>0.03422</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>0.060187</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0</v>
+        <v>0.314921</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0</v>
+        <v>0.310121</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0</v>
+        <v>0.310334</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0</v>
+        <v>0.310635</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0</v>
+        <v>0.31105</v>
       </c>
     </row>
     <row r="8">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.680183</v>
+        <v>0.753128</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.548605</v>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.680183</v>
+        <v>-0.753128</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>1.87545</v>
@@ -5741,7 +5741,7 @@
         <v>0.262131</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>-1.521968</v>
+        <v>-2.424055</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-1.521968</v>
@@ -17019,7 +17019,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -21272,7 +21276,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -22356,7 +22364,11 @@
           <t>Net income (loss) $ 238,834 $</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -30189,7 +30201,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -38518,7 +38534,11 @@
           <t>Director fees 31,564</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
@@ -43578,7 +43598,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E403" t="inlineStr">
         <is>
           <t>-</t>
@@ -43740,7 +43764,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E405" t="inlineStr">
         <is>
           <t>-</t>
